--- a/허브누리_레시피_목록_상세_p5of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p5of6_썸네일.xlsx
@@ -26701,7 +26701,15 @@
 섞어 바르면 검은 반점을 제거하며 얼굴을 윤기나게하여 안색을 좋게한다." 라고 되어있네요.</t>
         </is>
       </c>
-      <c r="H354" s="4" t="n"/>
+      <c r="H354" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 라벤더워터를 계량하세요.
+2. 워터를 가열 (60~70도) 살짝 식혀주세요.
+3. 팅크처, 히아루론산, 진주가루, 알부틴을 넣어주세요. (스킨용기에 라벤더워터를 담은 후 계량했어요)
+4. 완성~ (진주가루가 밑에 가루앉아 있기 때문에 사용하실 때마다 흔들어주세요.)</t>
+        </is>
+      </c>
       <c r="I354" s="4" t="n"/>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -27327,7 +27335,17 @@
 여성들에게는 너무 좋은 오일입니다. 노화, 주름관련효과있습니다.</t>
         </is>
       </c>
-      <c r="H376" s="7" t="n"/>
+      <c r="H376" s="7" t="inlineStr">
+        <is>
+          <t>만들기 순서
+1. 증류수를 계량 후 60~70도 데워주세요. 식혀주세요 (저온 살균하기 위해서랍니다.)
+2~3. 에센셜 오일이랑 올리브리퀴드를 계량한 후 스푼으로 섞어주세요
+4. 증류수를 부어주시구요.
+5. 저어주세요. (골고루 섞기 위해서 증류수를 부어주실 때는 2~3번 나누어서 부어주세요.)
+6. 히아루론산, 아카시아콜라겐 넣어주세요.
+(사용 후 좀더 보습을 원하시면 조금씩 히아루론산을 추가해주세요.)</t>
+        </is>
+      </c>
       <c r="I376" s="7" t="n"/>
       <c r="J376" s="6" t="inlineStr">
         <is>
@@ -27801,7 +27819,15 @@
 히비스커스 팅크처만 있으면 초간단만들기가 가능합니다.</t>
         </is>
       </c>
-      <c r="H394" s="7" t="n"/>
+      <c r="H394" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 로즈워터 계량하고
+2. 60~70도로 데워서 멸균하고
+3. 히비스커스 팅크쳐 넣고
+4. 히아루론산 넣으면 완성.</t>
+        </is>
+      </c>
       <c r="I394" s="7" t="n"/>
       <c r="J394" s="6" t="inlineStr">
         <is>
@@ -27911,7 +27937,16 @@
 칸데릴라왁스 사용시 밀랍 사용시</t>
         </is>
       </c>
-      <c r="H397" s="4" t="n"/>
+      <c r="H397" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 로즈힙오일, 카렌듈라오일, 스쿠알렌 계량해주고 (모두 액상상태인 것들입니다.)
+2. 식물성왁스인 칸데릴라왁스를 액상의 10%정도 양인 3그람 넣습니다.
+3. 액상오일+고체왁스 녹으면서 섞이는 중
+4. 온도가 50~40도 떨어지면 럭셔리 에센셜오일 첨가 후 섞기.
+5. 이쁜 용기에 담으면 완성.</t>
+        </is>
+      </c>
       <c r="I397" s="4" t="n"/>
       <c r="J397" s="3" t="inlineStr">
         <is>
@@ -33148,7 +33183,7 @@
       <c r="I564" s="8" t="n"/>
       <c r="J564" s="8" t="n"/>
     </row>
-    <row r="565" ht="16" customHeight="1">
+    <row r="565" ht="25" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
         <is>
           <t>자운고 인퓨즈 오일</t>
@@ -33180,7 +33215,16 @@
           <t>* 자운고 한방연고를 만들때 필요한 인퓨즈 오일 제조방법 입니다.</t>
         </is>
       </c>
-      <c r="H565" s="4" t="n"/>
+      <c r="H565" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+(정해진 비율은 없구요. 약재가 잠길 정도로 해주시면 되요. 오일을 한가지만 하셔도 되지만 여러가지 오일을 섞어서 사용하셔도 된답니다.)
+1. 8종 약재를 용기에 넣습니다. 유리용기 추천해요^^
+2. 골덴호호바오일 500g 부어줍니다.
+3-1. (온침법) 햇볕이 들어오는 창가에 두시고 2주 후면 완성. 생각날 때마다 흔들어주세요.
+3-2. (급속 온침법) 12~24시간 동안 40~50도 정도 온도를 유지하게 슬로우쿠커 등을 이용해 데워주세요. 급하게 재료 성분이 우러납니다.</t>
+        </is>
+      </c>
       <c r="I565" s="4" t="n"/>
       <c r="J565" s="3" t="inlineStr">
         <is>
@@ -33188,7 +33232,7 @@
         </is>
       </c>
     </row>
-    <row r="566" ht="16" customHeight="1">
+    <row r="566" ht="25" customHeight="1">
       <c r="C566" t="inlineStr">
         <is>
           <t>황금</t>
@@ -33205,7 +33249,7 @@
         </is>
       </c>
     </row>
-    <row r="567" ht="16" customHeight="1">
+    <row r="567" ht="25" customHeight="1">
       <c r="C567" t="inlineStr">
         <is>
           <t>유근피</t>
@@ -33222,7 +33266,7 @@
         </is>
       </c>
     </row>
-    <row r="568" ht="16" customHeight="1">
+    <row r="568" ht="25" customHeight="1">
       <c r="C568" t="inlineStr">
         <is>
           <t>금은화</t>
@@ -33239,7 +33283,7 @@
         </is>
       </c>
     </row>
-    <row r="569" ht="16" customHeight="1">
+    <row r="569" ht="25" customHeight="1">
       <c r="C569" t="inlineStr">
         <is>
           <t>감국</t>
@@ -33256,7 +33300,7 @@
         </is>
       </c>
     </row>
-    <row r="570" ht="16" customHeight="1">
+    <row r="570" ht="25" customHeight="1">
       <c r="C570" t="inlineStr">
         <is>
           <t>진피</t>
@@ -33273,7 +33317,7 @@
         </is>
       </c>
     </row>
-    <row r="571" ht="16" customHeight="1">
+    <row r="571" ht="25" customHeight="1">
       <c r="C571" t="inlineStr">
         <is>
           <t>자초</t>
@@ -33290,7 +33334,7 @@
         </is>
       </c>
     </row>
-    <row r="572" ht="16" customHeight="1">
+    <row r="572" ht="25" customHeight="1">
       <c r="C572" t="inlineStr">
         <is>
           <t>당귀</t>
@@ -33307,7 +33351,7 @@
         </is>
       </c>
     </row>
-    <row r="573" ht="16" customHeight="1">
+    <row r="573" ht="25" customHeight="1">
       <c r="C573" t="inlineStr">
         <is>
           <t>호호바오일</t>
@@ -34211,7 +34255,7 @@
         </is>
       </c>
     </row>
-    <row r="600" ht="35" customHeight="1">
+    <row r="600" ht="70" customHeight="1">
       <c r="A600" s="5" t="inlineStr">
         <is>
           <t>아로마솔트</t>
@@ -34242,7 +34286,17 @@
 주니퍼베리인 것 같아요. 해독효과가 탁월합니다.</t>
         </is>
       </c>
-      <c r="H600" s="7" t="n"/>
+      <c r="H600" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 소금을 계량합니다.
+2. 소금을 볶습니다. 볶으면 불필요한 수분이 날아가 유해성분도 날아가고 미네럴성분이 풍부해져요. 볶은 소금은 에센셜오일을 좌~~악 흡수하고, 아로마오일을 넣어도 소금이 녹지 않아요.
+3. 충분히 식힌 소금을 지퍼비닐에 넣고 쥬니퍼베리EO를 골고루 뿌려주세요.
+4. 봉지를 빵빵하게 해서 섞이게 흔들~흔들~ 어주세요.
+5. 레몬EO를 넣고 4번을 반복
+6. 적당량의 장미꽃잎을 넣고 섞어주면 완성됩니다.</t>
+        </is>
+      </c>
       <c r="I600" s="7" t="n"/>
       <c r="J600" s="6" t="inlineStr">
         <is>
@@ -34250,7 +34304,7 @@
         </is>
       </c>
     </row>
-    <row r="601" ht="35" customHeight="1">
+    <row r="601" ht="70" customHeight="1">
       <c r="A601" s="8" t="n"/>
       <c r="B601" s="8" t="n"/>
       <c r="C601" s="8" t="inlineStr">
@@ -34278,7 +34332,7 @@
       <c r="I601" s="8" t="n"/>
       <c r="J601" s="8" t="n"/>
     </row>
-    <row r="602" ht="35" customHeight="1">
+    <row r="602" ht="70" customHeight="1">
       <c r="A602" s="8" t="n"/>
       <c r="B602" s="8" t="n"/>
       <c r="C602" s="8" t="inlineStr">

--- a/허브누리_레시피_목록_상세_p5of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p5of6_썸네일.xlsx
@@ -464,7 +464,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="933450"/>
+    <ext cx="1047750" cy="923925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1689,7 +1689,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="62" name="Image 62" descr="Picture"/>
@@ -1864,7 +1864,7 @@
       <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="69" name="Image 69" descr="Picture"/>
@@ -2589,7 +2589,7 @@
       <row>74</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="98" name="Image 98" descr="Picture"/>
@@ -6564,7 +6564,7 @@
       <row>194</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="257" name="Image 257" descr="Picture"/>
@@ -9889,7 +9889,7 @@
       <row>402</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="657225" cy="1047750"/>
+    <ext cx="647700" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="390" name="Image 390" descr="Picture"/>
